--- a/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:37:07-05:00</t>
+    <t>2026-09-02T22:18:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2890" uniqueCount="495">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fhir/StructureDefinition/vax-dose</t>
+    <t>http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/vax-dose</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T22:18:14-04:00</t>
+    <t>2026-09-06T20:44:07-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -721,7 +721,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://fhirfli.dev/fhir/ig/cicada/ValueSet/eval-status</t>
+    <t>A set of codes indicating the current status of an Immunization.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1481,8 +1484,71 @@
     <t>The protocol (set of recommendations) being followed by the provider who administered the dose.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:doseNumberPositiveInt}
-</t>
+    <t>Immunization.protocolApplied.id</t>
+  </si>
+  <si>
+    <t>Immunization.protocolApplied.extension</t>
+  </si>
+  <si>
+    <t>Immunization.protocolApplied.modifierExtension</t>
+  </si>
+  <si>
+    <t>Immunization.protocolApplied.series</t>
+  </si>
+  <si>
+    <t>Name of vaccine series</t>
+  </si>
+  <si>
+    <t>One possible path to achieve presumed immunity against a disease - within the context of an authority.</t>
+  </si>
+  <si>
+    <t>Immunization.protocolApplied.authority</t>
+  </si>
+  <si>
+    <t>Who is responsible for publishing the recommendations</t>
+  </si>
+  <si>
+    <t>Indicates the authority who published the protocol (e.g. ACIP) that is being followed.</t>
+  </si>
+  <si>
+    <t>Immunization.protocolApplied.targetDisease</t>
+  </si>
+  <si>
+    <t>Vaccine preventatable disease being targetted</t>
+  </si>
+  <si>
+    <t>The vaccine preventable disease the dose is being administered against.</t>
+  </si>
+  <si>
+    <t>The vaccine preventable disease the dose is being administered for.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease|4.0.1</t>
+  </si>
+  <si>
+    <t>Immunization.protocolApplied.doseNumber[x]</t>
+  </si>
+  <si>
+    <t>positiveInt
+string</t>
+  </si>
+  <si>
+    <t>Dose number within series</t>
+  </si>
+  <si>
+    <t>Nominal position in a series.</t>
+  </si>
+  <si>
+    <t>The use of an integer is preferred if known. A string should only be used in cases where an integer is not available (such as when documenting a recurring booster dose).</t>
+  </si>
+  <si>
+    <t>Immunization.protocolApplied.seriesDoses[x]</t>
+  </si>
+  <si>
+    <t>Recommended number of doses for immunity</t>
+  </si>
+  <si>
+    <t>The recommended number of doses to achieve immunity.</t>
   </si>
 </sst>
 </file>
@@ -1784,11 +1850,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.09765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="36.85546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.46875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.62890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
@@ -1814,11 +1880,11 @@
     <col min="25" max="25" width="59.3515625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="55.8984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="27.6015625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.16015625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.3671875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="8.85546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.23828125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -4702,9 +4768,11 @@
       <c r="X25" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Y25" s="2"/>
+      <c r="Y25" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4737,16 +4805,16 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -4754,10 +4822,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4780,16 +4848,16 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4815,11 +4883,11 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4837,7 +4905,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4852,13 +4920,13 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4869,10 +4937,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4895,13 +4963,13 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4932,7 +5000,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4950,7 +5018,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>88</v>
@@ -4965,27 +5033,27 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5008,13 +5076,13 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5065,7 +5133,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>88</v>
@@ -5080,16 +5148,16 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5097,10 +5165,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5123,13 +5191,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5180,7 +5248,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5195,16 +5263,16 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5212,10 +5280,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5238,16 +5306,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5285,17 +5353,17 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>88</v>
@@ -5310,30 +5378,30 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
@@ -5355,16 +5423,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5414,7 +5482,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>88</v>
@@ -5429,27 +5497,27 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5472,13 +5540,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5529,7 +5597,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5550,10 +5618,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5561,10 +5629,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5587,16 +5655,16 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5646,7 +5714,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5664,13 +5732,13 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -5678,10 +5746,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5704,16 +5772,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5739,13 +5807,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5763,7 +5831,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5781,13 +5849,13 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -5795,10 +5863,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5821,13 +5889,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5878,7 +5946,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5893,16 +5961,16 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -5910,10 +5978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5936,13 +6004,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5993,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6011,24 +6079,24 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6051,13 +6119,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6108,7 +6176,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6126,24 +6194,24 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6166,13 +6234,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6223,7 +6291,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6241,10 +6309,10 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6255,10 +6323,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6281,13 +6349,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6314,13 +6382,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6338,7 +6406,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6356,24 +6424,24 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6396,13 +6464,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6429,13 +6497,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6453,7 +6521,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6471,24 +6539,24 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6511,13 +6579,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6568,7 +6636,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6586,10 +6654,10 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6600,10 +6668,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6626,13 +6694,13 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6683,7 +6751,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6698,13 +6766,13 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6715,10 +6783,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6741,13 +6809,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6798,7 +6866,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6819,7 +6887,7 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6830,10 +6898,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6859,10 +6927,10 @@
         <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>209</v>
@@ -6915,7 +6983,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6936,7 +7004,7 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6947,14 +7015,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6976,10 +7044,10 @@
         <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>209</v>
@@ -7034,7 +7102,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7066,10 +7134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7092,13 +7160,13 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7125,13 +7193,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7149,7 +7217,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7164,13 +7232,13 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7181,10 +7249,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7207,16 +7275,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7266,7 +7334,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>88</v>
@@ -7281,16 +7349,16 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7298,10 +7366,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7324,13 +7392,13 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7381,7 +7449,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7396,13 +7464,13 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7413,10 +7481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7439,13 +7507,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7472,13 +7540,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7496,7 +7564,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7511,13 +7579,13 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -7528,10 +7596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7554,13 +7622,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7611,7 +7679,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7626,7 +7694,7 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -7643,10 +7711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7669,23 +7737,23 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>20</v>
@@ -7730,7 +7798,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7748,7 +7816,7 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>131</v>
@@ -7762,10 +7830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7788,13 +7856,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7825,7 +7893,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7843,7 +7911,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7875,10 +7943,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7901,13 +7969,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7958,7 +8026,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7970,7 +8038,7 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -7990,10 +8058,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8016,13 +8084,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8073,7 +8141,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8094,7 +8162,7 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8105,10 +8173,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8134,10 +8202,10 @@
         <v>133</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>209</v>
@@ -8190,7 +8258,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8211,7 +8279,7 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8222,14 +8290,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8251,10 +8319,10 @@
         <v>133</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>209</v>
@@ -8309,7 +8377,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8341,10 +8409,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8367,13 +8435,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8424,7 +8492,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8442,7 +8510,7 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>131</v>
@@ -8456,10 +8524,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8485,10 +8553,10 @@
         <v>102</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8539,7 +8607,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8571,10 +8639,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8597,13 +8665,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8654,7 +8722,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8672,7 +8740,7 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>131</v>
@@ -8686,10 +8754,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8712,13 +8780,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8769,7 +8837,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8787,7 +8855,7 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>131</v>
@@ -8801,10 +8869,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8827,13 +8895,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8860,13 +8928,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8884,7 +8952,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8902,7 +8970,7 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>131</v>
@@ -8916,10 +8984,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8942,13 +9010,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8975,13 +9043,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -8999,7 +9067,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9031,10 +9099,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9057,16 +9125,16 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9116,7 +9184,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9134,10 +9202,10 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>20</v>
@@ -9148,10 +9216,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9174,13 +9242,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9231,7 +9299,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9252,7 +9320,7 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
@@ -9263,10 +9331,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9292,10 +9360,10 @@
         <v>133</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>209</v>
@@ -9348,7 +9416,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9369,7 +9437,7 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>20</v>
@@ -9380,14 +9448,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9409,10 +9477,10 @@
         <v>133</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>209</v>
@@ -9467,7 +9535,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9499,10 +9567,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9525,13 +9593,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9582,7 +9650,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9600,10 +9668,10 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>20</v>
@@ -9614,10 +9682,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9640,13 +9708,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9697,7 +9765,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9715,10 +9783,10 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
@@ -9729,10 +9797,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9755,13 +9823,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9812,7 +9880,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9830,10 +9898,10 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -9844,10 +9912,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9870,13 +9938,13 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9915,17 +9983,19 @@
         <v>20</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AC70" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9952,6 +10022,936 @@
         <v>20</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:44:07-04:00</t>
+    <t>2026-09-06T23:13:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T23:13:14-04:00</t>
+    <t>2026-09-07T18:40:23-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2890" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="427">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:40:23-04:00</t>
+    <t>2026-09-07T19:28:06-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Detailed information about each vaccination dose.</t>
+    <t>An administered dose as the engine reads it: the vaccine as CVX, the date, the patient, and optionally the dose volume, the manufacturer and a subpotency reason. The engine's evaluation of the dose is returned on ImmunizationEvaluation (target-dose-status-ext, evaluation-detail-ext), not written back onto the Immunization; until 2026-09-07 this profile declared thirteen evaluation extensions nothing ever emitted.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -425,21 +425,21 @@
     <t>Immunization.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -449,220 +449,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Immunization.extension:assessmentDate</t>
-  </si>
-  <si>
-    <t>assessmentDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/assessment-date}
-</t>
-  </si>
-  <si>
-    <t>The date on which the vaccination assessment was made.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Immunization.extension:inadvertentAdministration</t>
-  </si>
-  <si>
-    <t>inadvertentAdministration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/inadvertent-administration-status}
-</t>
-  </si>
-  <si>
-    <t>Inadvertent Administration Status</t>
-  </si>
-  <si>
-    <t>Indicates if the vaccine was administered inadvertently.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:validAgeStatus</t>
-  </si>
-  <si>
-    <t>validAgeStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/valid-age-status}
-</t>
-  </si>
-  <si>
-    <t>Valid Age Status</t>
-  </si>
-  <si>
-    <t>Indicates if the vaccine was administered at the correct age.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:validAgeReason</t>
-  </si>
-  <si>
-    <t>validAgeReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/valid-age-reason}
-</t>
-  </si>
-  <si>
-    <t>Valid Age Reason</t>
-  </si>
-  <si>
-    <t>Captures the reason why the vaccine was administered at a particular age.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:preferredIntervalStatus</t>
-  </si>
-  <si>
-    <t>preferredIntervalStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/preferred-interval-status}
-</t>
-  </si>
-  <si>
-    <t>Preferred Interval Status</t>
-  </si>
-  <si>
-    <t>Indicates if the vaccine was administered at the preferred interval.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:preferredIntervalReason</t>
-  </si>
-  <si>
-    <t>preferredIntervalReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/preferred-interval-reason}
-</t>
-  </si>
-  <si>
-    <t>Preferred Interval Reason</t>
-  </si>
-  <si>
-    <t>Captures the reason for the preferred interval between vaccine doses.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:allowedIntervalStatus</t>
-  </si>
-  <si>
-    <t>allowedIntervalStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/allowed-interval-status}
-</t>
-  </si>
-  <si>
-    <t>Allowed Interval Status</t>
-  </si>
-  <si>
-    <t>Captures the status of the allowed interval for vaccination.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:allowedIntervalReason</t>
-  </si>
-  <si>
-    <t>allowedIntervalReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/allowed-interval-reason}
-</t>
-  </si>
-  <si>
-    <t>Allowed Interval Reason</t>
-  </si>
-  <si>
-    <t>Captures the reason for the allowed interval between vaccine doses.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:vaccinationConflict</t>
-  </si>
-  <si>
-    <t>vaccinationConflict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/vaccination-conflict}
-</t>
-  </si>
-  <si>
-    <t>Vaccination Conflict</t>
-  </si>
-  <si>
-    <t>Indicates any conflicts with other vaccinations.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:preferredVaccineStatus</t>
-  </si>
-  <si>
-    <t>preferredVaccineStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/preferred-vaccine-status}
-</t>
-  </si>
-  <si>
-    <t>Preferred Vaccine Status</t>
-  </si>
-  <si>
-    <t>Indicates if the vaccine administered is the preferred vaccine.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:preferredVaccineReason</t>
-  </si>
-  <si>
-    <t>preferredVaccineReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/preferred-vaccine-reason}
-</t>
-  </si>
-  <si>
-    <t>Preferred Vaccine Reason</t>
-  </si>
-  <si>
-    <t>Captures the reason why a particular vaccine is preferred.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:allowedVaccineStatus</t>
-  </si>
-  <si>
-    <t>allowedVaccineStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/allowed-vaccine-status}
-</t>
-  </si>
-  <si>
-    <t>Allowed Vaccine Status</t>
-  </si>
-  <si>
-    <t>Indicates if the vaccine administered is allowed under certain conditions.</t>
-  </si>
-  <si>
-    <t>Immunization.extension:allowedVaccineReason</t>
-  </si>
-  <si>
-    <t>allowedVaccineReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/allowed-vaccine-reason}
-</t>
-  </si>
-  <si>
-    <t>Allowed Vaccine Reason</t>
-  </si>
-  <si>
-    <t>Captures the reason why a particular vaccine is allowed.</t>
-  </si>
-  <si>
     <t>Immunization.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -672,9 +459,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -1142,9 +926,6 @@
   </si>
   <si>
     <t>Immunization.performer.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1850,12 +1631,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO78"/>
+  <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.09765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.64453125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.46875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.62890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.265625" customWidth="true" bestFit="true"/>
@@ -1863,7 +1644,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.8984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="60.36328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2844,7 +2625,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2863,15 +2644,17 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>20</v>
@@ -2908,14 +2691,16 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>138</v>
@@ -2939,7 +2724,7 @@
         <v>20</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>20</v>
@@ -2953,41 +2738,43 @@
         <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -3035,7 +2822,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3044,7 +2831,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -3056,7 +2843,7 @@
         <v>20</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>20</v>
@@ -3070,11 +2857,9 @@
         <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
@@ -3083,7 +2868,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -3095,13 +2880,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3152,7 +2937,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3161,43 +2946,41 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>88</v>
@@ -3206,21 +2989,23 @@
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3245,13 +3030,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -3269,31 +3054,31 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>20</v>
@@ -3301,14 +3086,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>20</v>
       </c>
@@ -3329,15 +3112,17 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3362,13 +3147,11 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>20</v>
@@ -3386,28 +3169,28 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>20</v>
@@ -3418,20 +3201,18 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>88</v>
@@ -3443,16 +3224,16 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3479,13 +3260,11 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3503,52 +3282,50 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>88</v>
@@ -3560,16 +3337,16 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3620,31 +3397,31 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>20</v>
@@ -3652,14 +3429,12 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3680,13 +3455,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3737,31 +3512,31 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>20</v>
@@ -3769,20 +3544,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>88</v>
@@ -3794,18 +3567,20 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3842,64 +3617,62 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>20</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>88</v>
@@ -3911,18 +3684,20 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3971,46 +3746,44 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>20</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>20</v>
       </c>
@@ -4031,13 +3804,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4088,19 +3861,19 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>138</v>
+        <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -4109,10 +3882,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -4120,14 +3893,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4145,18 +3916,20 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4205,31 +3978,31 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -4237,14 +4010,12 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4265,15 +4036,17 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4298,13 +4071,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4322,31 +4095,31 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4354,14 +4127,12 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4382,13 +4153,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4439,31 +4210,31 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -4471,46 +4242,42 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4558,42 +4325,42 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>20</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4604,7 +4371,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4616,13 +4383,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4673,13 +4440,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4688,27 +4455,27 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>216</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>219</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4716,7 +4483,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>88</v>
@@ -4725,23 +4492,21 @@
         <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>108</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4766,13 +4531,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4790,10 +4555,10 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>88</v>
@@ -4805,16 +4570,16 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -4822,10 +4587,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4848,17 +4613,15 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4883,11 +4646,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4905,7 +4670,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4920,27 +4685,27 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4948,7 +4713,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
@@ -4960,16 +4725,16 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4996,11 +4761,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5018,10 +4785,10 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>88</v>
@@ -5033,27 +4800,27 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>247</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5061,7 +4828,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
@@ -5073,16 +4840,16 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5133,10 +4900,10 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>88</v>
@@ -5148,16 +4915,16 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5165,10 +4932,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5179,7 +4946,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5188,16 +4955,16 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5248,13 +5015,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5263,16 +5030,16 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5280,10 +5047,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5291,7 +5058,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>88</v>
@@ -5303,20 +5070,18 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5353,20 +5118,22 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>88</v>
@@ -5375,43 +5142,41 @@
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>274</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>275</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5420,19 +5185,19 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>268</v>
+        <v>137</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5482,74 +5247,78 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>274</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>275</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5597,19 +5366,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5618,10 +5387,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>282</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5629,10 +5398,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5655,17 +5424,15 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>284</v>
+        <v>164</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5690,13 +5457,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5714,7 +5481,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5729,16 +5496,16 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>288</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -5746,10 +5513,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5757,7 +5524,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
@@ -5769,19 +5536,19 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>231</v>
+        <v>310</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5807,13 +5574,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5831,10 +5598,10 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>88</v>
@@ -5846,16 +5613,16 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>288</v>
+        <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -5863,10 +5630,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5877,7 +5644,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5886,16 +5653,16 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5946,13 +5713,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5961,16 +5728,16 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -5978,10 +5745,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5992,7 +5759,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6004,13 +5771,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>308</v>
+        <v>164</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6037,13 +5804,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6061,13 +5828,13 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
@@ -6076,27 +5843,27 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6107,7 +5874,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6119,13 +5886,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6176,13 +5943,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -6191,27 +5958,27 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>20</v>
+        <v>334</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>318</v>
+        <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>319</v>
+        <v>131</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>320</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6228,26 +5995,30 @@
         <v>20</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>322</v>
+        <v>217</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q38" s="2"/>
+      <c r="Q38" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="R38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6291,7 +6062,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6309,10 +6080,10 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>326</v>
+        <v>131</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6323,10 +6094,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6337,7 +6108,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6349,13 +6120,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6382,13 +6153,11 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6406,13 +6175,13 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -6424,24 +6193,24 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>333</v>
+        <v>131</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>334</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6452,7 +6221,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6464,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6497,13 +6266,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>338</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6521,42 +6290,42 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>348</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>340</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6579,13 +6348,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>344</v>
+        <v>248</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>290</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
+        <v>291</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6636,7 +6405,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>292</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6648,16 +6417,16 @@
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6668,14 +6437,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6691,18 +6460,20 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>350</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>135</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6751,7 +6522,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>349</v>
+        <v>296</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6763,16 +6534,16 @@
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>355</v>
+        <v>293</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6783,42 +6554,46 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>315</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>357</v>
+        <v>299</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6866,19 +6641,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -6887,7 +6662,7 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6898,21 +6673,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6924,17 +6699,15 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>133</v>
+        <v>248</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6983,28 +6756,28 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -7015,46 +6788,42 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7102,19 +6871,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7134,10 +6903,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7157,16 +6926,16 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7193,13 +6962,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7217,7 +6986,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7232,13 +7001,13 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>375</v>
+        <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>376</v>
+        <v>131</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7249,10 +7018,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7260,7 +7029,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>88</v>
@@ -7272,20 +7041,18 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>378</v>
+        <v>198</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7334,10 +7101,10 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>88</v>
@@ -7349,16 +7116,16 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>20</v>
+        <v>366</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>383</v>
+        <v>131</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7366,10 +7133,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7389,16 +7156,16 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7425,13 +7192,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>20</v>
+        <v>370</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7449,7 +7216,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7464,13 +7231,13 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>389</v>
+        <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>391</v>
+        <v>131</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7481,10 +7248,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7495,7 +7262,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7507,13 +7274,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7540,13 +7307,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>295</v>
+        <v>228</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7564,13 +7331,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7579,13 +7346,13 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>398</v>
+        <v>131</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -7596,10 +7363,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7622,15 +7389,17 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>400</v>
+        <v>283</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7679,7 +7448,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7694,13 +7463,13 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>402</v>
+        <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>20</v>
+        <v>382</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>131</v>
+        <v>383</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -7711,10 +7480,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7731,30 +7500,26 @@
         <v>20</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>404</v>
+        <v>290</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q51" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>20</v>
       </c>
@@ -7798,7 +7563,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>403</v>
+        <v>292</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7810,16 +7575,16 @@
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>408</v>
+        <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>131</v>
+        <v>293</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>20</v>
@@ -7830,14 +7595,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7856,15 +7621,17 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>231</v>
+        <v>134</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>410</v>
+        <v>135</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7889,11 +7656,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7911,7 +7680,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>296</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7923,7 +7692,7 @@
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -7932,7 +7701,7 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>131</v>
+        <v>293</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -7943,14 +7712,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7963,22 +7732,26 @@
         <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>350</v>
+        <v>134</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>414</v>
+        <v>299</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8026,7 +7799,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>413</v>
+        <v>301</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8038,7 +7811,7 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>416</v>
+        <v>139</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8058,10 +7831,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8084,13 +7857,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>315</v>
+        <v>198</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>357</v>
+        <v>388</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8141,7 +7914,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8153,16 +7926,16 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>20</v>
+        <v>390</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>360</v>
+        <v>206</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8173,21 +7946,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8199,17 +7972,15 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>133</v>
+        <v>392</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>362</v>
+        <v>393</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8258,28 +8029,28 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>20</v>
+        <v>395</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8290,46 +8061,42 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>133</v>
+        <v>217</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -8377,28 +8144,28 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>131</v>
+        <v>401</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
@@ -8409,10 +8176,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8423,7 +8190,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8435,13 +8202,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8492,13 +8259,13 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
@@ -8510,7 +8277,7 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>131</v>
@@ -8524,10 +8291,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8550,13 +8317,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>102</v>
+        <v>248</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>425</v>
+        <v>290</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>426</v>
+        <v>291</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8607,7 +8374,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>424</v>
+        <v>292</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8619,7 +8386,7 @@
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -8628,7 +8395,7 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>131</v>
+        <v>293</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>20</v>
@@ -8639,21 +8406,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8665,15 +8432,17 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>428</v>
+        <v>135</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8722,28 +8491,28 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>427</v>
+        <v>296</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>131</v>
+        <v>293</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>20</v>
@@ -8754,42 +8523,46 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>432</v>
+        <v>299</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8837,25 +8610,25 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>431</v>
+        <v>301</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>131</v>
@@ -8869,10 +8642,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8883,7 +8656,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8895,13 +8668,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8928,13 +8701,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>438</v>
+        <v>20</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>439</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8952,13 +8725,13 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
@@ -8970,7 +8743,7 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>440</v>
+        <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>131</v>
@@ -8984,10 +8757,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9010,13 +8783,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9043,13 +8816,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -9067,7 +8840,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9099,10 +8872,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9125,17 +8898,15 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>350</v>
+        <v>164</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>415</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9160,13 +8931,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>20</v>
+        <v>417</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>20</v>
+        <v>418</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9184,7 +8955,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9202,10 +8973,10 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>450</v>
+        <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>451</v>
+        <v>131</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>20</v>
@@ -9216,10 +8987,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9227,7 +8998,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>88</v>
@@ -9242,15 +9013,17 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>315</v>
+        <v>420</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9299,10 +9072,10 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>88</v>
@@ -9311,7 +9084,7 @@
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9320,7 +9093,7 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
@@ -9331,21 +9104,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>453</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>453</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9357,16 +9130,16 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>133</v>
+        <v>420</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>362</v>
+        <v>425</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>363</v>
+        <v>426</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>209</v>
+        <v>423</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9416,19 +9189,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>364</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -9437,1521 +9210,12 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO78" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-vax-dose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T19:28:06-04:00</t>
+    <t>2026-09-07T19:51:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
